--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00138_18940629.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00138_18940629.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00138_18940629.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y53"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: best wishes of a large circle of friends.â€”</t>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: H. Scott, Caledonia, br. h.， Bryson.</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BEVERLYâ€™S APPEAL.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L29: isolated marker/symbol line :: A</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>989</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -696,12 +700,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L203: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CowiE.â€” In his city, on the 29th inst., Marion</t>
+          <t>L297: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Village Farm, b. h.， Rex Americus.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, June 29.â€”F. MacKelcan, Q.</t>
+          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ECKERT.—In Brantford, € nt., on the 28th inst,</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -779,12 +783,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L486: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pink crÃ©pon gowns and the maids of</t>
+          <t>L511: stray/suspicious non-ASCII glyph(s): U+76CA CJK UNIFIED IDEOGRAPH-76CA | isolated marker/symbol line :: 益</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: happy couple left on the 4 oâ€™clock train</t>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • One kiss before we part." "Wha—wha</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -808,7 +812,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L791: line starts with digit/letter garbage token | suspicious token(s): 1one (letter/digit mix) :: 1one or two gentlemen, in private family ;</t>
+          <t>L722: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • One kiss before we part." "Wha—wha</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -835,7 +839,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -854,12 +858,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN :: Pay a Compliment to an Oid HÃ¤mlton</t>
+          <t>L606: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON :: son, Brampton.:：</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: best wishes of a large circle of friends.â€”</t>
+          <t>L1195: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -883,7 +887,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L840: line starts with digit/letter garbage token | suspicious token(s): 1Pianoforte (letter/digit mix) :: 1Pianoforte tuner, 146 Hannah street east.</t>
+          <t>L791: line starts with digit/letter garbage token | suspicious token(s): 1one (letter/digit mix) :: 1one or two gentlemen, in private family ;</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -929,14 +933,10 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: é«˜</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: IN HYMENâ€™S BONDS.</t>
-        </is>
-      </c>
+          <t>L679: stray/suspicious non-ASCII glyph(s): U+9AD8 CJK UNIFIED IDEOGRAPH-9AD8 | isolated marker/symbol line :: 高</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L862: line starts with digit/letter garbage token | suspicious token(s): 1RS (letter/digit mix) :: 1RS. REECE, NO. 190 JAMES STREET</t>
+          <t>L840: line starts with digit/letter garbage token | suspicious token(s): 1Pianoforte (letter/digit mix) :: 1Pianoforte tuner, 146 Hannah street east.</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1004,14 +1004,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ï¿¥</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: umarried at the residence of the brideâ€™s</t>
-        </is>
-      </c>
+          <t>L828: stray/suspicious non-ASCII glyph(s): U+FFE5 FULLWIDTH YEN SIGN | isolated marker/symbol line :: ￥</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L1214: line starts with digit/letter garbage token | suspicious token(s): 1It (letter/digit mix) :: 1It is said that the most noted shot</t>
+          <t>L862: line starts with digit/letter garbage token | suspicious token(s): 1RS (letter/digit mix) :: 1RS. REECE, NO. 190 JAMES STREET</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1077,12 +1073,12 @@
           <t>L551: suspicious token(s): 170R (letter/digit mix) :: 170R SALE, THE "WEEKLY TIMES," 3</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00AC NOT SIGN :: ECKERT.â€”In Brantford, â‚¬ nt., on the 28th inst,</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>L957: stray/suspicious non-ASCII glyph(s): U+5C11 CJK UNIFIED IDEOGRAPH-5C11 | isolated marker/symbol line :: 少</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1102,7 +1098,11 @@
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L1214: line starts with digit/letter garbage token | suspicious token(s): 1It (letter/digit mix) :: 1It is said that the most noted shot</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1145,11 +1145,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: STOVE-TOWERS.â€”On June 28th, 1891. at the</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1189,12 +1185,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1212,11 +1208,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LOWE-BUTLER.â€”At the residence 9 of the bride's</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1261,7 +1253,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1279,11 +1271,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L333: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SCOTT.â€”At the residence of his brother-in-law,</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1323,12 +1311,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1346,11 +1334,7 @@
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: on arrival of 8 oâ€™clock train from Hamilton.</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1413,11 +1397,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MCMAHON.â€”On June 29th, at No. 92 Isabella</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1462,7 +1442,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1480,21 +1460,17 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L357: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cowie.â€”In this city, on the 29th inst., Marion</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L577: symbol-only separator/garbage line :: $400:</t>
+          <t>L511: stray/suspicious non-ASCII glyph(s): U+76CA CJK UNIFIED IDEOGRAPH-76CA | isolated marker/symbol line :: 益</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L1244: symbol-only separator/garbage line :: 82.60.</t>
+          <t>L1195: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •*</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1547,21 +1523,17 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HELP WANTEDâ€”MALE.</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L586: isolated marker/symbol line :: 111</t>
+          <t>L577: symbol-only separator/garbage line :: $400:</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L1265: isolated marker/symbol line :: *</t>
+          <t>L1244: symbol-only separator/garbage line :: 82.60.</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1610,19 +1582,19 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L447: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Beverly and East Flamboroâ€™ be raised $2</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L595: symbol-only separator/garbage line :: 1223</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr"/>
+          <t>L586: isolated marker/symbol line :: 111</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>L1265: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1669,16 +1641,12 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: THE TRADERSâ€™ BANK OF CANADA.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line :: 2454</t>
+          <t>L595: symbol-only separator/garbage line :: 1223</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr"/>
@@ -1712,16 +1680,12 @@
       </c>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ain grocery, fruit or confectionerâ€™s. Best</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: 7.</t>
+          <t>L607: symbol-only separator/garbage line :: 2454</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1755,16 +1719,12 @@
       </c>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: é«˜</t>
+          <t>L668: isolated marker/symbol line :: 7.</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr"/>
@@ -1798,16 +1758,12 @@
       </c>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ginning at 10 oâ€™clock in the morning.</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L696: symbol-only separator/garbage line :: 11.</t>
+          <t>L679: stray/suspicious non-ASCII glyph(s): U+9AD8 CJK UNIFIED IDEOGRAPH-9AD8 | isolated marker/symbol line :: 高</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1841,16 +1797,12 @@
       </c>
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L587: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mondayâ€™s match race is attracting</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L719: isolated marker/symbol line :: 4</t>
+          <t>L696: symbol-only separator/garbage line :: 11.</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1884,16 +1836,12 @@
       </c>
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: King, dam Minnequa Maid, by Woodâ€™s</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L723: isolated marker/symbol line :: a</t>
+          <t>L719: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1923,16 +1871,12 @@
       </c>
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York. June 29.â€”The weather at</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L818: isolated marker/symbol line :: 24</t>
+          <t>L723: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1962,16 +1906,12 @@
       </c>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: presents were magnificent. The brideâ€™s</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ï¿¥</t>
+          <t>L818: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -2001,16 +1941,12 @@
       </c>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tions- Cowen, Leoncavalloâ€™s ** Berceuse,</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L884: isolated marker/symbol line :: C</t>
+          <t>L828: stray/suspicious non-ASCII glyph(s): U+FFE5 FULLWIDTH YEN SIGN | isolated marker/symbol line :: ￥</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -2040,16 +1976,12 @@
       </c>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L714: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Sullivanâ€™s symphonies, in fact all the</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L952: isolated marker/symbol line :: P</t>
+          <t>L884: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -2075,16 +2007,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ One kiss before we part." "Whaâ€”wha</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L955: symbol-only separator/garbage line :: 62.60.</t>
+          <t>L952: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -2110,16 +2038,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”what ?" faltered the clerk, who ex-</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L957: isolated marker/symbol line :: å°‘</t>
+          <t>L955: symbol-only separator/garbage line :: 62.60.</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2145,16 +2069,12 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: pected anything but that. *â€˜One kiss</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L960: isolated marker/symbol line :: 2</t>
+          <t>L957: stray/suspicious non-ASCII glyph(s): U+5C11 CJK UNIFIED IDEOGRAPH-5C11 | isolated marker/symbol line :: 少</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2180,14 +2100,14 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: before we part,â€™ repeated the pretty pure</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>L960: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O30" s="1" t="inlineStr"/>
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr"/>
@@ -2200,719 +2120,6 @@
       <c r="X30" s="1" t="inlineStr"/>
       <c r="Y30" s="1" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”the Countess complained on account of</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr"/>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr"/>
-      <c r="U31" s="1" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
-      <c r="W31" s="1" t="inlineStr"/>
-      <c r="X31" s="1" t="inlineStr"/>
-      <c r="Y31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L772: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of fruit jars and rubbers.â€”Hazell &amp; Son,</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr"/>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr"/>
-      <c r="U32" s="1" t="inlineStr"/>
-      <c r="V32" s="1" t="inlineStr"/>
-      <c r="W32" s="1" t="inlineStr"/>
-      <c r="X32" s="1" t="inlineStr"/>
-      <c r="Y32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WAUGHâ€™S,</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L795: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 1 (shaded) park grounds, Elâ€™s nore, bay side,</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: TRY KELLYâ€™S NEW MIXED HARD-</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L842: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜Phone 1078. Office at râ€™amiltonâ€™s drug store.</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L847: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gentsâ€™ suit- ceaned this week, $1.25 dyed $1.75,</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L863: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: IVE north, has a large assortment of ladiesâ€™</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L864: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and childrenâ€™s spring dn s es for sale, new and</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜0 and 52 James street north.</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L933: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 1047.</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L937: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Orangeville, June 29.-The second dayâ€™s</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: money and J. W. Rattenburyâ€™s Hamlet</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L988: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: aid Smithâ€™s place. After dinner, in the</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1034: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: weâ€™ve got it. Frederick Lyonde, opposite</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1088: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: trees. American Plum, Plantersâ€™ Pride Pear,</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Menâ€™s singlesâ€”H. R. Barnard beat P.</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1195: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢*</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1224: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: limited number of pupils; own or pupilsâ€™ resi-</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1239: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: King street east, centre of Coppâ€™s block.</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CLINEâ€™S JUBILEE PARK.</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr"/>
-      <c r="R51" s="1" t="inlineStr"/>
-      <c r="S51" s="1" t="inlineStr"/>
-      <c r="T51" s="1" t="inlineStr"/>
-      <c r="U51" s="1" t="inlineStr"/>
-      <c r="V51" s="1" t="inlineStr"/>
-      <c r="W51" s="1" t="inlineStr"/>
-      <c r="X51" s="1" t="inlineStr"/>
-      <c r="Y51" s="1" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Dick Hicksâ€”Sometimes I wish I was</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr"/>
-      <c r="R52" s="1" t="inlineStr"/>
-      <c r="S52" s="1" t="inlineStr"/>
-      <c r="T52" s="1" t="inlineStr"/>
-      <c r="U52" s="1" t="inlineStr"/>
-      <c r="V52" s="1" t="inlineStr"/>
-      <c r="W52" s="1" t="inlineStr"/>
-      <c r="X52" s="1" t="inlineStr"/>
-      <c r="Y52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr"/>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: samples. Studio, 181 King cast, Coppâ€™s</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
-      <c r="R53" s="1" t="inlineStr"/>
-      <c r="S53" s="1" t="inlineStr"/>
-      <c r="T53" s="1" t="inlineStr"/>
-      <c r="U53" s="1" t="inlineStr"/>
-      <c r="V53" s="1" t="inlineStr"/>
-      <c r="W53" s="1" t="inlineStr"/>
-      <c r="X53" s="1" t="inlineStr"/>
-      <c r="Y53" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
